--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tab04_afford_summary.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tab04_afford_summary.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="A. Rate (%)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B. Gap (COP/day)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="B. Gap (FGT1, 0-1)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="C. Severity (FGT2, 0-1)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t xml:space="preserve">Table 4A. Unaffordability rate (%) by income decile, city and diet model, 2019–2024</t>
   </si>
@@ -51,19 +52,19 @@
     <t xml:space="preserve">2019–2024</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1 (21.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4 (19.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1 (19.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0 (12.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1 (7.2)</t>
+    <t xml:space="preserve">43.9 (22.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8 (19.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7 (19.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9 (13.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0 (7.5)</t>
   </si>
   <si>
     <t xml:space="preserve">99.4 (2.9)</t>
@@ -75,19 +76,19 @@
     <t xml:space="preserve">2019</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9 (10.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7 (5.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8 (12.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.0 (10.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3 (9.0)</t>
+    <t xml:space="preserve">29.2 (11.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7 (6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6 (12.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.9 (10.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7 (9.8)</t>
   </si>
   <si>
     <t xml:space="preserve">96.6 (6.6)</t>
@@ -96,58 +97,58 @@
     <t xml:space="preserve">2020</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4 (29.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.9 (30.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.5 (23.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3 (11.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9 (10.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8 (0.6)</t>
+    <t xml:space="preserve">72.5 (30.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6 (29.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8 (23.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1 (11.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8 (11.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9 (0.5)</t>
   </si>
   <si>
     <t xml:space="preserve">2021</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5 (13.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9 (9.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8 (16.7)</t>
+    <t xml:space="preserve">52.4 (14.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9 (8.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3 (17.3)</t>
   </si>
   <si>
     <t xml:space="preserve">2022</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5 (10.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9 (7.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4 (11.7)</t>
+    <t xml:space="preserve">47.4 (10.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0 (7.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9 (11.8)</t>
   </si>
   <si>
     <t xml:space="preserve">2023</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7 (10.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1 (17.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7 (13.5)</t>
+    <t xml:space="preserve">38.4 (10.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0 (13.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1 (13.8)</t>
   </si>
   <si>
     <t xml:space="preserve">98.2 (4.9)</t>
@@ -156,49 +157,49 @@
     <t xml:space="preserve">2024</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8 (5.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8 (10.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5 (12.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3 (15.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5 (8.1)</t>
+    <t xml:space="preserve">23.7 (5.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7 (10.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4 (14.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9 (15.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4 (8.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 2</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8 (20.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4 (10.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2 (21.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3 (30.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6 (30.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7 (33.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3 (13.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0 (14.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1 (4.2)</t>
+    <t xml:space="preserve">4.9 (20.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6 (10.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2 (21.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5 (30.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8 (30.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8 (33.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4 (13.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1 (14.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1 (4.4)</t>
   </si>
   <si>
     <t xml:space="preserve">0.0 (0.0)</t>
@@ -207,316 +208,313 @@
     <t xml:space="preserve">0.4 (1.3)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9 (5.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2 (13.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5 (19.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7 (14.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9 (9.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0 (44.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4 (22.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9 (45.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1 (38.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3 (41.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4 (32.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6 (11.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0 (23.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8 (18.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4 (15.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5 (23.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4 (13.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5 (18.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8 (22.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5 (16.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8 (33.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7 (7.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0 (3.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9 (2.1)</t>
+    <t xml:space="preserve">2.9 (6.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9 (13.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4 (18.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3 (13.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7 (10.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1 (44.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3 (23.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1 (46.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9 (38.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0 (40.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.8 (32.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3 (12.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1 (23.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1 (18.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6 (15.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9 (22.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8 (13.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6 (17.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3 (21.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3 (15.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4 (34.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0 (6.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1 (3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 (1.9)</t>
   </si>
   <si>
     <t xml:space="preserve">11.9 (15.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">82.3 (18.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0 (15.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3 (16.0)</t>
+    <t xml:space="preserve">81.9 (18.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.6 (15.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0 (15.7)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8 (5.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8 (9.8)</t>
+    <t xml:space="preserve">0.9 (5.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0 (10.5)</t>
   </si>
   <si>
     <t xml:space="preserve">5.6 (23.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0 (21.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8 (28.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3 (39.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0 (36.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1 (25.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8 (13.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2 (11.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0 (20.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9 (12.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6 (22.7)</t>
+    <t xml:space="preserve">6.1 (20.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2 (28.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3 (39.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4 (35.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2 (25.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0 (13.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3 (11.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3 (21.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3 (13.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8 (24.2)</t>
   </si>
   <si>
     <t xml:space="preserve">33.3 (49.2)</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8 (43.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8 (45.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9 (35.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6 (39.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7 (20.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3 (24.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9 (2.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4 (21.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1 (3.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4 (11.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3 (16.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0 (19.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 (5.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4 (20.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1 (22.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5 (28.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9 (19.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6 (16.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0 (26.0)</t>
+    <t xml:space="preserve">32.4 (42.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6 (45.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8 (36.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0 (38.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0 (20.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3 (23.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8 (3.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7 (20.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0 (3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9 (12.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0 (16.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6 (18.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9 (6.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1 (22.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1 (21.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7 (29.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0 (19.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0 (16.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1 (25.9)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 4</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4 (10.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6 (3.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9 (20.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6 (26.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1 (24.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1 (37.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4 (23.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3 (8.0)</t>
+    <t xml:space="preserve">2.4 (10.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5 (26.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9 (24.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3 (37.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4 (23.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2 (7.8)</t>
   </si>
   <si>
     <t xml:space="preserve">29.4 (44.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1 (47.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2 (48.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2 (40.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9 (23.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1 (33.5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4 (7.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1 (6.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1 (23.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4 (13.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3 (17.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0 (21.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4 (26.5)</t>
+    <t xml:space="preserve">42.9 (47.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3 (48.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5 (40.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7 (23.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7 (33.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1 (6.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7 (5.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5 (22.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 (13.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5 (16.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4 (21.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6 (26.2)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 5</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 (6.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2 (21.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7 (12.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7 (24.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2 (14.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1 (46.4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5 (26.1)</t>
+    <t xml:space="preserve">1.0 (6.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1 (21.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8 (12.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9 (24.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9 (14.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8 (46.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6 (26.6)</t>
   </si>
   <si>
     <t xml:space="preserve">34.2 (48.7)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6 (15.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7 (13.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7 (6.4)</t>
+    <t xml:space="preserve">4.4 (15.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3 (13.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 (8.2)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 6</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 (5.9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6 (16.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3 (13.8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7 (35.8)</t>
+    <t xml:space="preserve">1.1 (6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7 (16.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7 (15.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3 (36.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 7</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6 (4.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6 (9.5)</t>
+    <t xml:space="preserve">0.6 (3.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 (9.2)</t>
   </si>
   <si>
     <t xml:space="preserve">Decil 8</t>
@@ -531,13 +529,961 @@
     <t xml:space="preserve">Note: Mean (SD) across monthly observations. Bold = full-period mean (2019–2024).</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 4B. Affordability gap (COP/day) by income decile, city and diet model, 2019–2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 (0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (0)</t>
+    <t xml:space="preserve">Table 4B. Affordability gap (FGT1, 0–1) by income decile, city and diet model, 2019–2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248 (0.191)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.216 (0.154)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276 (0.182)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460 (0.179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472 (0.142)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575 (0.136)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640 (0.123)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626 (0.102)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703 (0.096)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137 (0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152 (0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.184 (0.056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285 (0.069)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352 (0.054)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420 (0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509 (0.053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535 (0.046)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593 (0.061)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520 (0.326)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414 (0.280)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528 (0.310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674 (0.260)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623 (0.225)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723 (0.192)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783 (0.176)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729 (0.166)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805 (0.136)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267 (0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.185 (0.038)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270 (0.102)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539 (0.087)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471 (0.049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573 (0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.694 (0.058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625 (0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700 (0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.237 (0.063)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180 (0.053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.206 (0.090)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506 (0.061)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487 (0.059)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531 (0.080)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.671 (0.056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.198 (0.046)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236 (0.078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245 (0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434 (0.071)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514 (0.096)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598 (0.053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658 (0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718 (0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129 (0.040)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128 (0.074)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.221 (0.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321 (0.070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388 (0.107)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607 (0.071)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572 (0.073)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731 (0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.020 (0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 (0.030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024 (0.106)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060 (0.148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054 (0.112)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143 (0.159)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264 (0.164)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238 (0.135)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368 (0.148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000 (0.000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 (0.002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010 (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.096 (0.044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120 (0.200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142 (0.232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.247 (0.298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.192 (0.222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307 (0.300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447 (0.261)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360 (0.232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493 (0.241)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.063 (0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118 (0.084)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342 (0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242 (0.046)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363 (0.077)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.037 (0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272 (0.049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343 (0.046)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055 (0.059)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.197 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.257 (0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279 (0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436 (0.038)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009 (0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141 (0.063)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140 (0.054)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163 (0.075)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403 (0.057)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017 (0.073)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033 (0.099)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107 (0.131)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079 (0.103)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.207 (0.138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 (0.006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022 (0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103 (0.157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.056 (0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147 (0.211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258 (0.229)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179 (0.190)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324 (0.225)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011 (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060 (0.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.199 (0.076)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111 (0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.096 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.190 (0.049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029 (0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.092 (0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109 (0.079)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277 (0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009 (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.233 (0.054)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000 (0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022 (0.077)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013 (0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060 (0.098)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 (0.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.050 (0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117 (0.162)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.071 (0.101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160 (0.195)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011 (0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (0.053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 (0.001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 (0.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.085 (0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055 (0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 (0.004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014 (0.057)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.052 (0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.080 (0.124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021 (0.040)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 4C. Affordability severity (FGT2, 0–1) by income decile, city and diet model, 2019–2024. Squared gap, giving greater weight to households furthest from threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.191 (0.183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156 (0.133)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.197 (0.179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313 (0.183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306 (0.146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393 (0.162)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457 (0.161)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435 (0.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525 (0.137)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.096 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103 (0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123 (0.038)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.208 (0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.252 (0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305 (0.056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331 (0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389 (0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448 (0.330)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324 (0.251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448 (0.324)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559 (0.301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481 (0.252)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591 (0.263)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662 (0.249)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582 (0.223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683 (0.211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.194 (0.070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121 (0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178 (0.083)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355 (0.089)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379 (0.099)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510 (0.078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515 (0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132 (0.074)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321 (0.063)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295 (0.058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330 (0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482 (0.055)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474 (0.076)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145 (0.037)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172 (0.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152 (0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335 (0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392 (0.063)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432 (0.053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468 (0.083)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533 (0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.095 (0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.097 (0.061)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147 (0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.201 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.231 (0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411 (0.074)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352 (0.055)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366 (0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555 (0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011 (0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013 (0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028 (0.103)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018 (0.059)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.052 (0.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103 (0.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081 (0.093)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163 (0.134)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017 (0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021 (0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.041 (0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.064 (0.114)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013 (0.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078 (0.139)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150 (0.219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.090 (0.124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.184 (0.244)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269 (0.254)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.187 (0.180)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302 (0.259)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028 (0.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126 (0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.068 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143 (0.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 (0.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016 (0.013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101 (0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.083 (0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125 (0.031)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010 (0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.049 (0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.076 (0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.091 (0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.195 (0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032 (0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029 (0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039 (0.026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 (0.027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031 (0.071)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.019 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.065 (0.084)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036 (0.059)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.065 (0.104)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.119 (0.145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.068 (0.087)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155 (0.170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.034 (0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008 (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048 (0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.019 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042 (0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015 (0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021 (0.020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.082 (0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060 (0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007 (0.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015 (0.042)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011 (0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.040 (0.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016 (0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.062 (0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 (0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012 (0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 (0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 (0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010 (0.019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021 (0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000 (0.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.006)</t>
   </si>
 </sst>
 </file>
@@ -1789,16 +2735,16 @@
         <v>128</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="26">
@@ -1853,22 +2799,22 @@
         <v>62</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="J27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="K27" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="28">
@@ -1897,13 +2843,13 @@
         <v>62</v>
       </c>
       <c r="I28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="29">
@@ -1932,13 +2878,13 @@
         <v>62</v>
       </c>
       <c r="I29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J29" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="30">
@@ -1967,13 +2913,13 @@
         <v>62</v>
       </c>
       <c r="I30" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="K30" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="31">
@@ -2008,12 +2954,12 @@
         <v>62</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -2034,21 +2980,21 @@
         <v>62</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>19</v>
@@ -2083,7 +3029,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>26</v>
@@ -2104,21 +3050,21 @@
         <v>62</v>
       </c>
       <c r="H34" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="J34" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="K34" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>33</v>
@@ -2148,12 +3094,12 @@
         <v>62</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>37</v>
@@ -2188,7 +3134,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>41</v>
@@ -2218,12 +3164,12 @@
         <v>62</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>46</v>
@@ -2253,12 +3199,12 @@
         <v>62</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>11</v>
@@ -2282,18 +3228,18 @@
         <v>62</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>19</v>
@@ -2328,7 +3274,7 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>26</v>
@@ -2352,18 +3298,18 @@
         <v>62</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>33</v>
@@ -2398,7 +3344,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>37</v>
@@ -2433,7 +3379,7 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>41</v>
@@ -2468,7 +3414,7 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>46</v>
@@ -2503,7 +3449,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>11</v>
@@ -2533,12 +3479,12 @@
         <v>62</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>19</v>
@@ -2573,7 +3519,7 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>26</v>
@@ -2603,12 +3549,12 @@
         <v>62</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>33</v>
@@ -2643,7 +3589,7 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>37</v>
@@ -2678,7 +3624,7 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>41</v>
@@ -2713,7 +3659,7 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>46</v>
@@ -2748,7 +3694,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>11</v>
@@ -2783,7 +3729,7 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>19</v>
@@ -2818,7 +3764,7 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>26</v>
@@ -2853,7 +3799,7 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>33</v>
@@ -2888,7 +3834,7 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>37</v>
@@ -2923,7 +3869,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>41</v>
@@ -2958,7 +3904,7 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>46</v>
@@ -2993,7 +3939,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>11</v>
@@ -3028,7 +3974,7 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>19</v>
@@ -3063,7 +4009,7 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>26</v>
@@ -3098,7 +4044,7 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>33</v>
@@ -3133,7 +4079,7 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>37</v>
@@ -3168,7 +4114,7 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>41</v>
@@ -3203,7 +4149,7 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>46</v>
@@ -3238,7 +4184,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>11</v>
@@ -3273,7 +4219,7 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>19</v>
@@ -3308,7 +4254,7 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>26</v>
@@ -3343,7 +4289,7 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>33</v>
@@ -3378,7 +4324,7 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>37</v>
@@ -3413,7 +4359,7 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>41</v>
@@ -3448,7 +4394,7 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>46</v>
@@ -3483,7 +4429,7 @@
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3519,7 +4465,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
@@ -3600,31 +4546,31 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>173</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -3635,31 +4581,31 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -3670,31 +4616,31 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -3705,31 +4651,31 @@
         <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
@@ -3740,31 +4686,31 @@
         <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
@@ -3775,31 +4721,31 @@
         <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
@@ -3810,31 +4756,31 @@
         <v>46</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>173</v>
+        <v>228</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -3845,31 +4791,31 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>173</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -3880,31 +4826,31 @@
         <v>19</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>173</v>
+        <v>248</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
@@ -3915,31 +4861,31 @@
         <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14">
@@ -3950,31 +4896,31 @@
         <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
@@ -3985,31 +4931,31 @@
         <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>173</v>
+        <v>266</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16">
@@ -4020,31 +4966,31 @@
         <v>41</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>173</v>
+        <v>274</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>173</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17">
@@ -4055,31 +5001,31 @@
         <v>46</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>173</v>
+        <v>278</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>173</v>
+        <v>280</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>173</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18">
@@ -4090,31 +5036,31 @@
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>173</v>
+        <v>283</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>173</v>
+        <v>284</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>173</v>
+        <v>286</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>173</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19">
@@ -4125,31 +5071,31 @@
         <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>173</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20">
@@ -4160,31 +5106,31 @@
         <v>26</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>173</v>
+        <v>293</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>173</v>
+        <v>296</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>173</v>
+        <v>297</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>173</v>
+        <v>298</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>173</v>
+        <v>299</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>173</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21">
@@ -4195,31 +5141,31 @@
         <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>173</v>
+        <v>301</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>173</v>
+        <v>303</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>173</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22">
@@ -4230,31 +5176,31 @@
         <v>37</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>173</v>
+        <v>307</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>173</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23">
@@ -4265,31 +5211,31 @@
         <v>41</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>173</v>
+        <v>309</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>173</v>
+        <v>310</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>173</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24">
@@ -4300,31 +5246,31 @@
         <v>46</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>173</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25">
@@ -4335,31 +5281,31 @@
         <v>11</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>173</v>
+        <v>319</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>173</v>
+        <v>320</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>173</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26">
@@ -4370,31 +5316,31 @@
         <v>19</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27">
@@ -4405,31 +5351,31 @@
         <v>26</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>173</v>
+        <v>323</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>173</v>
+        <v>324</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>173</v>
+        <v>326</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>173</v>
+        <v>327</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28">
@@ -4440,31 +5386,31 @@
         <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>173</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29">
@@ -4475,31 +5421,31 @@
         <v>37</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>173</v>
+        <v>331</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30">
@@ -4510,31 +5456,31 @@
         <v>41</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>173</v>
+        <v>333</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>173</v>
+        <v>334</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>173</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31">
@@ -4545,1506 +5491,4067 @@
         <v>46</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>173</v>
+        <v>337</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>173</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>173</v>
+        <v>339</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>173</v>
+        <v>340</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>173</v>
+        <v>323</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>173</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>173</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>173</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>173</v>
+        <v>337</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>173</v>
+        <v>343</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>173</v>
+        <v>344</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>173</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>173</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>173</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A74:K74"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
